--- a/data/trans_orig/IP31KM04_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM04_2023-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6664</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3504</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11398</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>6983</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3478</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>13797</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8409</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>2261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15394</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>11746</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9423</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>64417</t>
+          <t>53599</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57603</t>
+          <t>48865</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67922</t>
+          <t>56759</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66198</t>
+          <t>49840</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59213</t>
+          <t>46228</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70220</t>
+          <t>52661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>130614</t>
+          <t>103440</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121266</t>
+          <t>97292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136584</t>
+          <t>107732</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71400</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74607</t>
+          <t>54922</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>146007</t>
+          <t>115186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>35770</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26728</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>45343</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>31,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>23,25%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>39,45%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>36969</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15948</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>51677</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>29,42%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>41,13%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>33798</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30354</t>
+          <t>25849</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51512</t>
+          <t>42090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>76702</t>
+          <t>69568</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53361</t>
+          <t>56771</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93590</t>
+          <t>82749</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79181</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69608</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>88223</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>68,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>60,55%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>76,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>88680</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73972</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>109701</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>70,58%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>58,87%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,31%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>86690</t>
+          <t>65535</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74911</t>
+          <t>57243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96069</t>
+          <t>73484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>57,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>175369</t>
+          <t>144716</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158481</t>
+          <t>131535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198710</t>
+          <t>157513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>61,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>73,51%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>114951</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126423</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>252071</t>
+          <t>214284</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17652</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12216</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23016</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>21,32%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,17%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12935</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8575</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18465</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>15,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>20067</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26856</t>
+          <t>17351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>33002</t>
+          <t>29916</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25614</t>
+          <t>22893</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41247</t>
+          <t>37302</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,48%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>39647</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34283</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>45083</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>69,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,83%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>78,68%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>42617</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>37087</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>46977</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>76,72%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>66,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>84,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>44566</t>
+          <t>41848</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37777</t>
+          <t>36761</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50201</t>
+          <t>46310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>67,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>87183</t>
+          <t>81495</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78938</t>
+          <t>74109</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>94571</t>
+          <t>88518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>57299</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>55552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>64633</t>
+          <t>54112</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120185</t>
+          <t>111411</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36498</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26737</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49121</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>52,28%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>70,36%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>25891</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>18915</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>33315</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>37,16%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40879</t>
+          <t>26004</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54910</t>
+          <t>34603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>66771</t>
+          <t>62502</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>53271</t>
+          <t>49509</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86148</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>33318</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>20695</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>43079</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>47,72%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>29,64%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>61,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>43791</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>36367</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>50767</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>62,84%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>52,19%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>34488</t>
+          <t>44458</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>35859</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45344</t>
+          <t>50703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>63,1%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>78278</t>
+          <t>77776</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>58901</t>
+          <t>61904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91778</t>
+          <t>90769</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>69816</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>69682</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75367</t>
+          <t>70462</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>145049</t>
+          <t>140278</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>37554</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>34497</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>39014</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>94,88%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>87,16%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>98,57%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>31752</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>28827</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33331</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>92,84%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>84,29%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>97,46%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>33019</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>35453</t>
+          <t>29897</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40186</t>
+          <t>34583</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>70276</t>
+          <t>70573</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66394</t>
+          <t>66964</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72702</t>
+          <t>72881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>89,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>565</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5082</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12,84%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2448</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5373</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>7,16%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>15,71%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>787</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5473</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>74919</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>8724</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5127</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>13192</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>18,48%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10,86%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>27,94%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>6538</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3581</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>10723</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>14,76%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6719</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>3583</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>10877</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>15,17%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>8,09%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>24,21%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>10306</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>6281</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>15183</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>19,16%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>15443</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>10563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>21654</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -2548,74 +2548,74 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>38485</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>34017</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>42082</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>81,52%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>72,06%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>89,14%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>37752</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>33567</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>40709</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>85,24%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>75,79%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>37567</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>33409</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>40703</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>84,83%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>75,44%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>91,91%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>43476</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>38599</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>47501</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>80,84%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>71,77%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>88,32%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>133</t>
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>81228</t>
+          <t>76052</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>74436</t>
+          <t>69841</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>86148</t>
+          <t>80932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,46%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>47209</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>44290</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>53782</t>
+          <t>44286</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>98072</t>
+          <t>91495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>73778</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>62035</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>85375</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>52,48%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>44,13%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>60,73%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>78538</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>68833</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>87636</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>63,49%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>55,65%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>70,85%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>85674</t>
+          <t>76768</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>73403</t>
+          <t>66898</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98409</t>
+          <t>85670</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>164212</t>
+          <t>150547</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>148397</t>
+          <t>135833</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>180494</t>
+          <t>165072</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>66793</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>55196</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>78536</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>47,52%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>39,27%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>55,87%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>45158</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>36060</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>54863</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>36,51%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>29,15%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>44,35%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>69370</t>
+          <t>45054</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56635</t>
+          <t>36152</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>81641</t>
+          <t>54924</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>114528</t>
+          <t>111847</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>98246</t>
+          <t>97322</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>130343</t>
+          <t>126561</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>42,63%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>48,23%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140571</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>123696</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155044</t>
+          <t>121822</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>278740</t>
+          <t>262394</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>103658</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>93040</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>113915</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>65,97%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>59,21%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>72,49%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>78457</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>68758</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>86978</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>60,98%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>53,44%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>67,6%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>102922</t>
+          <t>82936</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>91911</t>
+          <t>72225</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>112059</t>
+          <t>92522</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>181378</t>
+          <t>186594</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166450</t>
+          <t>172611</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>194591</t>
+          <t>200051</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>67,81%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>53478</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>43221</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>64096</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>34,03%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>27,51%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>40,79%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>50208</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>41687</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>59907</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>39,02%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>32,4%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>46,56%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>51237</t>
+          <t>54964</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>42100</t>
+          <t>45378</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62248</t>
+          <t>65675</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>101445</t>
+          <t>108442</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>88232</t>
+          <t>94985</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>116373</t>
+          <t>122425</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,5%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>157136</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>128665</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>137900</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>282823</t>
+          <t>295036</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>320299</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>298651</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>346673</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>46,63%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>50,47%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>408</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>278064</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>241923</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>304384</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>42,57%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>37,04%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>46,6%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>346514</t>
+          <t>276591</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>316080</t>
+          <t>254684</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>374094</t>
+          <t>298384</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>624578</t>
+          <t>596889</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>579463</t>
+          <t>564640</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>663286</t>
+          <t>630113</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>43,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>47,45%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>366525</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>340151</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>388173</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>53,37%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>49,53%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>56,52%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>375070</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>348750</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>411211</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>57,43%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>53,4%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>62,96%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>398219</t>
+          <t>341617</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>370639</t>
+          <t>319824</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>428653</t>
+          <t>363524</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>773289</t>
+          <t>708142</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>734581</t>
+          <t>674918</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>818404</t>
+          <t>740391</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>56,73%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
